--- a/artfynd/A 44098-2026 artfynd.xlsx
+++ b/artfynd/A 44098-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137454499</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137454510</v>
       </c>
       <c r="B3" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137454515</v>
       </c>
       <c r="B4" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>137454511</v>
       </c>
       <c r="B5" t="n">
-        <v>97544</v>
+        <v>97548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137454509</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>137454512</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137454517</v>
       </c>
       <c r="B8" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137454513</v>
       </c>
       <c r="B9" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
